--- a/Kalkulationstool/vergleich/Vergleich_Excel_HTML.xlsx
+++ b/Kalkulationstool/vergleich/Vergleich_Excel_HTML.xlsx
@@ -818,7 +818,7 @@
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>Währung: Die Testdatei rechnet in CHF (1 EUR = 0,94 CHF). Die OtO-Werte in EUR sind die CHF-Werte ÷ 0,94, z. B. Angebots-TO 4,114,331.78 EUR; das ändert die Kalkulation nicht und ist im Vergleich nicht enthalten.</t>
+          <t>Währung: Testdatei und Vergleich in EUR (Standard). Bei Kalkulation in HUF oder GBP ändern sich nur die OtO-Werte: sie werden mit dem Kurs 1 EUR = x in EUR umgerechnet.</t>
         </is>
       </c>
     </row>

--- a/Kalkulationstool/vergleich/Vergleich_Excel_HTML.xlsx
+++ b/Kalkulationstool/vergleich/Vergleich_Excel_HTML.xlsx
@@ -541,22 +541,22 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>3818013.24980544</v>
+        <v>3896572.98793965</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>3818013.249805439</v>
+        <v>3896572.987939645</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>3867471.868581444</v>
+        <v>3948448.829427472</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>49458.61877600383</v>
+        <v>51875.84148782166</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.01295401967987517</v>
+        <v>0.01331319640319416</v>
       </c>
     </row>
     <row r="6">
@@ -566,22 +566,22 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>3588932.45481711</v>
+        <v>3662778.60866327</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>3588932.454817113</v>
+        <v>3662778.608663267</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>3635423.556466558</v>
+        <v>3711541.899661824</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>46491.10164944734</v>
+        <v>48763.29099855386</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>0.01295401967987623</v>
+        <v>0.01331319640319457</v>
       </c>
     </row>
     <row r="7">
@@ -591,22 +591,22 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3373596.50752809</v>
+        <v>3443011.89214347</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>3373596.507528086</v>
+        <v>3443011.892143471</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>3441638.001220771</v>
+        <v>3513189.243824321</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>68041.49369268073</v>
+        <v>70177.35168085108</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>0.02016882977583358</v>
+        <v>0.02038254699061225</v>
       </c>
     </row>
     <row r="8">
@@ -616,22 +616,22 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>3032647.92432046</v>
+        <v>3095047.92432046</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>3032647.92432046</v>
+        <v>3095047.92432046</v>
       </c>
       <c r="D8" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>3203628.923376535</v>
+        <v>3267948.923376535</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>170980.9990560752</v>
+        <v>172900.9990560752</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>0.05638010191848689</v>
+        <v>0.05586375503185041</v>
       </c>
     </row>
     <row r="9">
@@ -641,22 +641,22 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>19090066.2490272</v>
+        <v>19482864.9396982</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>19090066.2490272</v>
+        <v>19482864.93969823</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>19337359.34290722</v>
+        <v>19742244.14713736</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>247293.0938800238</v>
+        <v>259379.2074391618</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>0.01295401967987542</v>
+        <v>0.01331319640319694</v>
       </c>
     </row>
     <row r="10">
@@ -666,22 +666,22 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>408527.417729182</v>
+        <v>416933.309709542</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>408527.4177291821</v>
+        <v>416933.309709542</v>
       </c>
       <c r="D10" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>400780.2802191756</v>
+        <v>409444.8150297005</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>-7747.137510006432</v>
+        <v>-7488.494679841504</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>-0.01896356810778881</v>
+        <v>-0.01796089327825208</v>
       </c>
     </row>
     <row r="11">
@@ -691,22 +691,22 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>694878.41146459</v>
+        <v>709176.283805016</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>694878.41146459</v>
+        <v>709176.2838050154</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>588682.1837804141</v>
+        <v>603055.5943305839</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-106196.2276841759</v>
+        <v>-106120.689474432</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>-0.152827064321004</v>
+        <v>-0.1496393659768935</v>
       </c>
     </row>
     <row r="12">
@@ -716,22 +716,22 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>448616.556852139</v>
+        <v>457847.326082908</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>448616.5568521392</v>
+        <v>457847.3260829083</v>
       </c>
       <c r="D12" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>356633.8716655274</v>
+        <v>366148.6645649357</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>-91982.6851866116</v>
+        <v>-91698.66151797236</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>-0.2050363139337465</v>
+        <v>-0.2002821820594566</v>
       </c>
     </row>
     <row r="13">
@@ -741,22 +741,22 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>168472.730272717</v>
+        <v>171939.238298495</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>168472.7302727166</v>
+        <v>171939.2382984951</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>163450.0530037328</v>
+        <v>166872.3632343225</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>-5022.677268984204</v>
+        <v>-5066.875064172462</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>-0.02981299858353155</v>
+        <v>-0.02946898633676693</v>
       </c>
     </row>
     <row r="14">
@@ -766,17 +766,17 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.107</v>
+        <v>0.1069999999999999</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>0.107</v>
       </c>
       <c r="D14" s="7" t="n"/>
       <c r="E14" s="9" t="n">
-        <v>0.1036284926789082</v>
+        <v>0.103697637405895</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>-0.003371507321091774</v>
+        <v>-0.003302362594104866</v>
       </c>
       <c r="G14" s="7" t="n"/>
     </row>
@@ -790,18 +790,18 @@
     <row r="17" ht="32" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>Ergebnis 2: Im korrigierten Modus liegt der Angebots-TO der Testkalkulation um +49,458.62 € p.a. (+1.30%) über der Excel. Das Delta setzt sich aus gegenläufigen Effekten zusammen (Blatt „Überleitung“).</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="32" customHeight="1">
+          <t>Ergebnis 2: Im korrigierten Modus liegt der Angebots-TO der Testkalkulation um +51.875,84 € p.a. (+1,33 %) über der Excel. Das Delta setzt sich aus gegenläufigen Effekten zusammen (Blatt „Überleitung“).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>Größte Treiber: Zuschlag je Zeile (+48.910 €), Hochlauf und Volumenwachstum (+93.129 €), Sachkostensteigerung (+72.894 €) und Kalkulationszins (+29.994 €) erhöhen; Durchreichposten (−165.801 €), Tariferhöhung zum Stichtag (−27.298 €) und Beitragsbemessungsgrenzen (−5.885 €) senken.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="32" customHeight="1">
+          <t>Treiber des Deltas (Umsatz p.a., Blatt „Überleitung“): Durchreichposten mit eigenem Aufschlag -165.801 €; Hochlauf im ersten Jahr und Volumenwachstum +93.129 €; Sachkostensteigerung +72.894 €; Zuschlag je Zeile +48.910 €; Kalkulationszins auf Einmalkosten +39.668 €; Tariferhöhung zum Stichtag und Sätze je Jahr -27.298 €; Abschreibung, Beschaffung und Restbuchwert -7.256 €; Beitragsbemessungsgrenzen -5.885 €; FTE je Kalenderjahr +3.687 €; korrigierte Rechenlogik -171 €.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="45" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
         <is>
           <t>Gross Profit: Die Excel schlägt HV und BU als Anteil auf den Umsatz mit Verhandlung auf, das HTML-Tool nimmt die tatsächlich kalkulierten HV- und BU-Umlagen (Basis Umsatz ohne Verhandlung, ohne Durchreichposten). Dazu kommen die geringeren Umlagen durch Durchreichposten.</t>
@@ -984,31 +984,31 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>173481.2</v>
+        <v>235881.2</v>
       </c>
       <c r="C4" s="8" t="n">
-        <v>173481.2</v>
+        <v>235881.2</v>
       </c>
       <c r="D4" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>194842.9060065384</v>
+        <v>259162.9060065384</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>21361.70600653841</v>
+        <v>23281.70600653841</v>
       </c>
       <c r="G4" s="9" t="n">
-        <v>0.1231355674651686</v>
+        <v>0.09870098170832781</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>867406</v>
+        <v>1179406</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>974214.5300326921</v>
+        <v>1295814.530032692</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>106808.5300326921</v>
+        <v>116408.530032692</v>
       </c>
     </row>
     <row r="5">
@@ -1120,31 +1120,31 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>3032647.92432046</v>
+        <v>3095047.92432046</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>3032647.92432046</v>
+        <v>3095047.92432046</v>
       </c>
       <c r="D8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>3203628.923376535</v>
+        <v>3267948.923376535</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>170980.9990560752</v>
+        <v>172900.9990560752</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>0.05638010191848689</v>
+        <v>0.05586375503185041</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>15163239.6216023</v>
+        <v>15475239.6216023</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>16018144.61688268</v>
+        <v>16339744.61688268</v>
       </c>
       <c r="J8" s="12" t="n">
-        <v>854904.9952803757</v>
+        <v>864504.9952803757</v>
       </c>
     </row>
     <row r="9">
@@ -1154,31 +1154,31 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>340948.583207626</v>
+        <v>347963.96782301</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>340948.5832076258</v>
+        <v>347963.9678230104</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>238009.0778442354</v>
+        <v>245240.3204477857</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>-102939.5053633906</v>
+        <v>-102723.6473752243</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>-0.3019209066509126</v>
+        <v>-0.2952134613761909</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>1704742.91603813</v>
+        <v>1739819.83911505</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>1190045.389221177</v>
+        <v>1226201.602238929</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>-514697.5268169527</v>
+        <v>-513618.2368761213</v>
       </c>
     </row>
     <row r="10">
@@ -1188,31 +1188,31 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>3373596.50752809</v>
+        <v>3443011.89214347</v>
       </c>
       <c r="C10" s="12" t="n">
-        <v>3373596.507528086</v>
+        <v>3443011.892143471</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>3441638.001220771</v>
+        <v>3513189.243824321</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>68041.49369268073</v>
+        <v>70177.35168085108</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>0.02016882977583358</v>
+        <v>0.02038254699061225</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>16867982.5376404</v>
+        <v>17215059.4607174</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v>17208190.00610385</v>
+        <v>17565946.21912161</v>
       </c>
       <c r="J10" s="12" t="n">
-        <v>340207.4684634544</v>
+        <v>350886.7584042065</v>
       </c>
     </row>
     <row r="11">
@@ -1222,31 +1222,31 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>179446.622740856</v>
+        <v>183138.930433163</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>179446.6227408557</v>
+        <v>183138.9304331633</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>125267.9357074923</v>
+        <v>129073.8528672556</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-54178.68703336368</v>
+        <v>-54065.07756590738</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>-0.3019209066509135</v>
+        <v>-0.2952134613761904</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>897233.113704278</v>
+        <v>915694.652165817</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>626339.6785374617</v>
+        <v>645369.2643362782</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>-270893.4351668163</v>
+        <v>-270325.3878295388</v>
       </c>
     </row>
     <row r="12">
@@ -1256,31 +1256,31 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>35889.3245481711</v>
+        <v>36627.7860866327</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>35889.32454817113</v>
+        <v>36627.78608663267</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>25053.58714149846</v>
+        <v>25814.77057345113</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>-10835.73740667264</v>
+        <v>-10813.01551318158</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>-0.3019209066509116</v>
+        <v>-0.2952134613761923</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>179446.622740856</v>
+        <v>183138.930433163</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>125267.9357074923</v>
+        <v>129073.8528672556</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>-54178.68703336366</v>
+        <v>-54065.07756590737</v>
       </c>
     </row>
     <row r="13">
@@ -1290,31 +1290,31 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>3588932.45481711</v>
+        <v>3662778.60866327</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>3588932.454817113</v>
+        <v>3662778.608663267</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>3635423.556466558</v>
+        <v>3711541.899661824</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>46491.10164944734</v>
+        <v>48763.29099855386</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>0.01295401967987623</v>
+        <v>0.01331319640319457</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>17944662.2740856</v>
+        <v>18313893.0433163</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>18177117.78233279</v>
+        <v>18557709.49830912</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>232455.5082471892</v>
+        <v>243816.4549928196</v>
       </c>
     </row>
     <row r="14">
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>229080.794988326</v>
+        <v>233794.379276379</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>229080.7949883264</v>
+        <v>233794.3792763787</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>232048.3121148866</v>
+        <v>236906.9297656483</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>2967.517126560648</v>
+        <v>3112.550489269313</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>0.01295401967987702</v>
+        <v>0.01331319640319422</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>1145403.97494163</v>
+        <v>1168971.89638189</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>1160241.560574433</v>
+        <v>1184534.648828242</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>14837.58563280338</v>
+        <v>15562.75244635181</v>
       </c>
     </row>
     <row r="15">
@@ -1358,31 +1358,31 @@
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>3818013.24980544</v>
+        <v>3896572.98793965</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>3818013.249805439</v>
+        <v>3896572.987939645</v>
       </c>
       <c r="D15" s="12" t="n">
         <v>-0</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>3867471.868581444</v>
+        <v>3948448.829427472</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>49458.61877600383</v>
+        <v>51875.84148782166</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>0.01295401967987517</v>
+        <v>0.01331319640319416</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>19090066.2490272</v>
+        <v>19482864.9396982</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>19337359.34290722</v>
+        <v>19742244.14713736</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>247293.0938800238</v>
+        <v>259379.2074391618</v>
       </c>
     </row>
     <row r="16">
@@ -1392,22 +1392,22 @@
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>408527.417729182</v>
+        <v>416933.309709542</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>408527.4177291821</v>
+        <v>416933.309709542</v>
       </c>
       <c r="D16" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>400780.2802191756</v>
+        <v>409444.8150297005</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>-7747.137510006432</v>
+        <v>-7488.494679841504</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>-0.01896356810778881</v>
+        <v>-0.01796089327825208</v>
       </c>
     </row>
     <row r="17">
@@ -1417,22 +1417,22 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>694878.41146459</v>
+        <v>709176.283805016</v>
       </c>
       <c r="C17" s="8" t="n">
-        <v>694878.41146459</v>
+        <v>709176.2838050154</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>588682.1837804141</v>
+        <v>603055.5943305839</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-106196.2276841759</v>
+        <v>-106120.689474432</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>-0.152827064321004</v>
+        <v>-0.1496393659768935</v>
       </c>
     </row>
     <row r="18">
@@ -1442,22 +1442,22 @@
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>448616.556852139</v>
+        <v>457847.326082908</v>
       </c>
       <c r="C18" s="8" t="n">
-        <v>448616.5568521392</v>
+        <v>457847.3260829083</v>
       </c>
       <c r="D18" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>356633.8716655274</v>
+        <v>366148.6645649357</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>-91982.6851866116</v>
+        <v>-91698.66151797236</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>-0.2050363139337465</v>
+        <v>-0.2002821820594566</v>
       </c>
     </row>
     <row r="19">
@@ -1467,22 +1467,22 @@
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>168472.730272717</v>
+        <v>171939.238298495</v>
       </c>
       <c r="C19" s="8" t="n">
-        <v>168472.7302727166</v>
+        <v>171939.2382984951</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>163450.0530037328</v>
+        <v>166872.3632343225</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>-5022.677268984204</v>
+        <v>-5066.875064172462</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>-0.02981299858353155</v>
+        <v>-0.02946898633676693</v>
       </c>
     </row>
   </sheetData>
@@ -1497,7 +1497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -1572,21 +1572,21 @@
         </is>
       </c>
       <c r="B4" s="12" t="n">
-        <v>3818013.24980544</v>
+        <v>3896572.98793965</v>
       </c>
       <c r="C4" s="12" t="n"/>
       <c r="D4" s="12" t="n">
-        <v>19090066.2490272</v>
+        <v>19482864.9396982</v>
       </c>
       <c r="E4" s="12" t="n"/>
       <c r="F4" s="12" t="n">
-        <v>3373596.50752809</v>
+        <v>3443011.89214347</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>408527.417729182</v>
+        <v>416933.309709542</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>694878.41146459</v>
+        <v>709176.283805016</v>
       </c>
       <c r="I4" s="12" t="n"/>
     </row>
@@ -1597,28 +1597,28 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>3818013.249805439</v>
+        <v>3896572.987939645</v>
       </c>
       <c r="C5" s="8" t="n">
         <v>-0</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>19090066.2490272</v>
+        <v>19482864.93969823</v>
       </c>
       <c r="E5" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>3373596.507528086</v>
+        <v>3443011.892143471</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>408527.4177291821</v>
+        <v>416933.309709542</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>694878.41146459</v>
+        <v>709176.2838050154</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="6">
@@ -1628,28 +1628,28 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>3866923.176817099</v>
+        <v>3945482.914951305</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>48909.92701165983</v>
+        <v>48909.9270116603</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>19334615.8840855</v>
+        <v>19727414.57475653</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>244549.6350582987</v>
+        <v>244549.6350583024</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>3416813.319035589</v>
+        <v>3486228.703650974</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>413760.7799194296</v>
+        <v>422166.6718997897</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>703780.0181807121</v>
+        <v>718077.8905211376</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>8901.606716122129</v>
+        <v>8901.606716122245</v>
       </c>
     </row>
     <row r="7">
@@ -1659,28 +1659,28 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3866752.462763717</v>
+        <v>3945312.200897923</v>
       </c>
       <c r="C7" s="8" t="n">
         <v>-170.7140533821657</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>19333762.31381858</v>
+        <v>19726561.00448962</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>-853.5702669173479</v>
+        <v>-853.5702669136226</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>3416662.47609802</v>
+        <v>3486077.860713405</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>413742.5135157177</v>
+        <v>422148.4054960778</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>686348.5621405598</v>
+        <v>700292.9156593814</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>-17431.45604015235</v>
+        <v>-17784.9748617562</v>
       </c>
     </row>
     <row r="8">
@@ -1690,28 +1690,28 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>3860867.387725144</v>
+        <v>3939427.12585935</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>-5885.075038573239</v>
+        <v>-5885.075038573705</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>19304336.93862572</v>
+        <v>19697135.62929675</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>-29425.37519286573</v>
+        <v>-29425.37519286945</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>3411462.423793937</v>
+        <v>3480877.808409322</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>413112.8104865904</v>
+        <v>421518.7024669504</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>685303.961321213</v>
+        <v>699248.3148400346</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>-1044.600819346728</v>
+        <v>-1044.600819346844</v>
       </c>
     </row>
     <row r="9">
@@ -1721,28 +1721,28 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>3833568.896865923</v>
+        <v>3912128.63500013</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>-27298.49085922027</v>
+        <v>-27298.4908592198</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>19167844.48432961</v>
+        <v>19560643.17500065</v>
       </c>
       <c r="E9" s="8" t="n">
         <v>-136492.4542961009</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>3387341.47727073</v>
+        <v>3456756.861886115</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>410191.8719646538</v>
+        <v>418597.7639450139</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>680458.4791937014</v>
+        <v>694402.8327125232</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>-4845.482127511641</v>
+        <v>-4845.482127511408</v>
       </c>
     </row>
     <row r="10">
@@ -1752,28 +1752,28 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>3926697.750040242</v>
+        <v>4005257.488174448</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>93128.85317431903</v>
+        <v>93128.85317431856</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>19633488.75020121</v>
+        <v>20026287.44087224</v>
       </c>
       <c r="E10" s="8" t="n">
         <v>465644.2658715956</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>3469630.131935558</v>
+        <v>3539045.516550942</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>420156.659254306</v>
+        <v>428562.551234666</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>696988.8506321432</v>
+        <v>710933.2041509646</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>16530.3714384418</v>
+        <v>16530.37143844145</v>
       </c>
     </row>
     <row r="11">
@@ -1783,28 +1783,28 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>3930385.154755709</v>
+        <v>4008944.892889915</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>3687.404715466313</v>
+        <v>3687.404715466779</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>19651925.77377854</v>
+        <v>20044724.46444958</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>18437.0235773325</v>
+        <v>18437.02357733622</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>3472888.322742144</v>
+        <v>3542303.707357529</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>420551.2115588608</v>
+        <v>428957.103539221</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>697643.3649691383</v>
+        <v>711587.7184879601</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>654.514336995082</v>
+        <v>654.5143369954312</v>
       </c>
     </row>
     <row r="12">
@@ -1814,25 +1814,25 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>4003278.995367862</v>
+        <v>4081838.733502069</v>
       </c>
       <c r="C12" s="8" t="n">
         <v>72893.84061215352</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>20016394.97683932</v>
+        <v>20409193.66751035</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>364469.2030607723</v>
+        <v>364469.2030607685</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>3537297.320307043</v>
+        <v>3606712.704922428</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>428350.8525043613</v>
+        <v>436756.7444847214</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>710582.0216777956</v>
+        <v>724526.3751966173</v>
       </c>
       <c r="I12" s="8" t="n">
         <v>12938.65670865728</v>
@@ -1845,239 +1845,283 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>4033273.225955603</v>
+        <v>4121506.46202488</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>29994.23058774043</v>
+        <v>39667.72852281108</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>20166366.12977801</v>
+        <v>20607532.3101244</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>149971.1529386975</v>
+        <v>198338.6426140554</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>3563800.22245437</v>
+        <v>3641763.109845183</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>431560.2351772495</v>
+        <v>441001.1914366621</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>715905.9976071196</v>
+        <v>731567.3970094161</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>5323.97592932405</v>
+        <v>7041.021812798805</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
+          <t>+ Abschreibung, Beschaffung und Restbuchwert (Kauf ab Jahr 2, Miete)</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>4114250.186801631</v>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>-7256.275223249104</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>20571250.93400815</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>-36281.37611624971</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>3635351.465057921</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>440224.7699877744</v>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>730279.4081572895</v>
+      </c>
+      <c r="I14" s="8" t="n">
+        <v>-1287.98885212664</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
           <t>+ Durchreichposten mit eigenem Aufschlag</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n">
-        <v>3867471.868581444</v>
-      </c>
-      <c r="C14" s="8" t="n">
+      <c r="B15" s="8" t="n">
+        <v>3948448.829427472</v>
+      </c>
+      <c r="C15" s="8" t="n">
         <v>-165801.3573741587</v>
       </c>
-      <c r="D14" s="8" t="n">
-        <v>19337359.34290722</v>
-      </c>
-      <c r="E14" s="8" t="n">
+      <c r="D15" s="8" t="n">
+        <v>19742244.14713736</v>
+      </c>
+      <c r="E15" s="8" t="n">
         <v>-829006.7868707888</v>
       </c>
-      <c r="F14" s="8" t="n">
-        <v>3441638.001220771</v>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>400780.2802191756</v>
-      </c>
-      <c r="H14" s="8" t="n">
-        <v>588682.1837804141</v>
-      </c>
-      <c r="I14" s="8" t="n">
+      <c r="F15" s="8" t="n">
+        <v>3513189.243824321</v>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>409444.8150297005</v>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>603055.5943305839</v>
+      </c>
+      <c r="I15" s="8" t="n">
         <v>-127223.8138267056</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>Ergebnis: HTML korrigiert, vollständige Testdatei</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n">
-        <v>3867471.868581444</v>
-      </c>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n">
-        <v>19337359.34290722</v>
-      </c>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="12" t="n">
-        <v>3441638.001220771</v>
-      </c>
-      <c r="G15" s="12" t="n">
-        <v>400780.2802191756</v>
-      </c>
-      <c r="H15" s="12" t="n">
-        <v>588682.1837804141</v>
-      </c>
-      <c r="I15" s="12" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="B16" s="12" t="n">
+        <v>3948448.829427472</v>
+      </c>
+      <c r="C16" s="12" t="n"/>
+      <c r="D16" s="12" t="n">
+        <v>19742244.14713736</v>
+      </c>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="12" t="n">
+        <v>3513189.243824321</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>409444.8150297005</v>
+      </c>
+      <c r="H16" s="12" t="n">
+        <v>603055.5943305839</v>
+      </c>
+      <c r="I16" s="12" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Δ gesamt HTML korrigiert zu Excel</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n">
-        <v>49458.61877600383</v>
-      </c>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="5" t="n">
-        <v>247293.0938800238</v>
-      </c>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="5" t="n">
-        <v>68041.49369268073</v>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>-7747.137510006432</v>
-      </c>
-      <c r="H16" s="5" t="n">
-        <v>-106196.2276841759</v>
-      </c>
-      <c r="I16" s="4" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="B17" s="5" t="n">
+        <v>51875.84148782166</v>
+      </c>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="5" t="n">
+        <v>259379.2074391618</v>
+      </c>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="5" t="n">
+        <v>70177.35168085108</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-7488.494679841504</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-106120.689474432</v>
+      </c>
+      <c r="I17" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Merkmal</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Erläuterung</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>Zuschlag je Zeile</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>Staplerfahrer +12,5 % Schicht-/Nachtzuschlag. Das Excel kennt keinen Zuschlag je Qualifikation; der Wert wirkt im HTML-Tool in beiden Modi.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>Korrigierte Rechenlogik</t>
+          <t>Zuschlag je Zeile</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Monatsanteile je Kalenderjahr tagesgenau statt gerundet, gleiche Laufzeit für Personal- und Sachkosten, Gross Profit mit HV und BU auf den Umsatz ohne Verhandlung.</t>
+          <t>Staplerfahrer +12,5 % Schicht-/Nachtzuschlag. Das Excel kennt keinen Zuschlag je Qualifikation; der Wert wirkt im HTML-Tool in beiden Modi.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>Beitragsbemessungsgrenzen</t>
+          <t>Korrigierte Rechenlogik</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>KV/PV und RV/AV nur bis zur Grenze des Jahresentgelts je FTE; betrifft hohe Gehälter (Standortleitung).</t>
+          <t>Monatsanteile je Kalenderjahr tagesgenau statt gerundet, gleiche Laufzeit für Personal- und Sachkosten, Gross Profit mit HV und BU auf den Umsatz ohne Verhandlung.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>Tariferhöhung zum Stichtag</t>
+          <t>Beitragsbemessungsgrenzen</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Erhöhung zum Juli statt zum Jahresanfang, eigene Sätze 2028 (3,5 %) und 2030 (2,0 %) statt pauschal 3,0 %.</t>
+          <t>KV/PV und RV/AV nur bis zur Grenze des Jahresentgelts je FTE; betrifft hohe Gehälter (Standortleitung).</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>Hochlauf und Volumenwachstum</t>
+          <t>Tariferhöhung zum Stichtag</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>80 % der FTE im ersten Kalenderjahr, danach +3 % je Jahr. Im Excel bleiben die FTE über die Laufzeit konstant.</t>
+          <t>Erhöhung zum Juli statt zum Jahresanfang, eigene Sätze 2028 (3,5 %) und 2030 (2,0 %) statt pauschal 3,0 %.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>FTE je Kalenderjahr</t>
+          <t>Hochlauf und Volumenwachstum</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Disposition 2027 mit 1 FTE und 2031 mit 2 FTE statt 1,5.</t>
+          <t>80 % der FTE im ersten Kalenderjahr, danach +3 % je Jahr. Im Excel bleiben die FTE über die Laufzeit konstant.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>Sachkostensteigerung</t>
+          <t>FTE je Kalenderjahr</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Betriebskosten, Nachunternehmer und Einmalkosten +2 % je Jahr; im Excel ohne Steigerung.</t>
+          <t>Disposition 2027 mit 1 FTE und 2031 mit 2 FTE statt 1,5.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>Kalkulationszins</t>
+          <t>Sachkostensteigerung</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Investitionen und Ramp-up als Annuität mit 4 % Zins statt linear ohne Kapitalkosten.</t>
+          <t>Betriebskosten, Nachunternehmer und Einmalkosten +2 % je Jahr; im Excel ohne Steigerung.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
         <is>
+          <t>Kalkulationszins</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>Investitionen und Ramp-up als Annuität mit 4 % Zins statt linear ohne Kapitalkosten.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>Abschreibung und Restbuchwert</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Regalerweiterung: Kauf im zweiten Vertragsjahr, 8 Jahre Nutzungsdauer, Restwert 20.000 €; der übrige Restbuchwert wird im letzten Jahr abgeschrieben. Mietpool: Miete über 7 Jahre, vollständig in der Laufzeit angesetzt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
           <t>Durchreichposten</t>
         </is>
       </c>
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>Hallenmiete und Wachdienst nur mit 4 % Aufschlag statt Umlagen, Gewinn, Risiko und Verhandlung im Hundert. Senkt Preis, Umlagen und Marge deutlich.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="B21:I21"/>
+    <mergeCell ref="B29:I29"/>
     <mergeCell ref="B25:I25"/>
     <mergeCell ref="B24:I24"/>
     <mergeCell ref="B20:I20"/>
+    <mergeCell ref="B28:I28"/>
     <mergeCell ref="B22:I22"/>
-    <mergeCell ref="B19:I19"/>
     <mergeCell ref="B23:I23"/>
     <mergeCell ref="B27:I27"/>
     <mergeCell ref="B26:I26"/>
@@ -2832,7 +2876,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Nicht im Excel abbildbar: Zuschlag je Zeile, Beitragsbemessungsgrenzen, Tariferhöhung zum Stichtag und je Jahr, Hochlauf, Volumenwachstum, FTE je Jahr, Sachkostensteigerung, Kalkulationszins, Durchreichposten, Kalkulationswährung.</t>
+          <t>Nicht im Excel abbildbar: Zuschlag je Zeile, Beitragsbemessungsgrenzen, Tariferhöhung zum Stichtag und je Jahr, Hochlauf, Volumenwachstum, FTE je Jahr, Sachkostensteigerung, Kalkulationszins, Abschreibung mit Beschaffung, Startjahr, Nutzungsdauer und Restwert, Durchreichposten, Kalkulationswährung.</t>
         </is>
       </c>
     </row>
@@ -2935,7 +2979,7 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Lagertechnik lt. Stückliste (Lagerplaner): 1 × 850,000.00 €; IT-Ausstattung: 12 × 1,450.50 €</t>
+          <t>Lagertechnik lt. Stückliste (Lagerplaner): 1 × 850,000.00 €; IT-Ausstattung: 12 × 1,450.50 €; Regalerweiterung Halle 2: 1 × 240,000.00 €; Flurförderzeuge Mietpool: 2 × 36,000.00 €</t>
         </is>
       </c>
     </row>
